--- a/datasets/bird_species_new_add.xlsx
+++ b/datasets/bird_species_new_add.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dazedinthecity/Documents/GitHub/ceu-ds-project-groupB-2026/datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B87D3C-417D-5B4E-AE0C-77AB20D07631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{580210C9-7A73-B742-A52B-A2CF041427C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" xr2:uid="{9B1C65BD-926B-4948-96E7-D8EAAD009C24}"/>
+    <workbookView xWindow="0" yWindow="800" windowWidth="33280" windowHeight="21440" xr2:uid="{9B1C65BD-926B-4948-96E7-D8EAAD009C24}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -369,12 +369,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -389,11 +395,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -755,62 +764,62 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="6" t="s">
         <v>17</v>
       </c>
     </row>
